--- a/prioridade_amostragem.xlsx
+++ b/prioridade_amostragem.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MiguelSantos\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8811A2-17BD-46B0-AE33-C532CD0F64A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9A8811A2-17BD-46B0-AE33-C532CD0F64A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78E0AF77-91CF-4DA4-A939-84DC417363FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B5430E7-AEDF-4B80-93B9-7517FDD28347}"/>
   </bookViews>
